--- a/data/gravel/Mason ISO 2025.xlsx
+++ b/data/gravel/Mason ISO 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10727"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10921"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F30124A-B293-F448-954A-EB5261787073}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7AC416B-A873-C343-A44A-DAAFCBCD3A20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3060" yWindow="500" windowWidth="25740" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -263,9 +263,6 @@
     <t>Mason</t>
   </si>
   <si>
-    <t>pounds</t>
-  </si>
-  <si>
     <t>50CM</t>
   </si>
   <si>
@@ -420,6 +417,9 @@
   </si>
   <si>
     <t>rear_axle_spec</t>
+  </si>
+  <si>
+    <t>GBP</t>
   </si>
 </sst>
 </file>
@@ -815,7 +815,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.3">
@@ -839,7 +839,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.3">
@@ -847,7 +847,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C7" s="1"/>
       <c r="D7" s="1"/>
@@ -860,22 +860,22 @@
         <v>6</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C8" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="D8" s="4" t="s">
         <v>112</v>
       </c>
-      <c r="D8" s="4" t="s">
-        <v>113</v>
-      </c>
       <c r="E8" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="F8" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="F8" s="4" t="s">
+      <c r="G8" s="4" t="s">
         <v>78</v>
-      </c>
-      <c r="G8" s="4" t="s">
-        <v>79</v>
       </c>
       <c r="H8" s="4"/>
       <c r="I8" s="4"/>
@@ -888,10 +888,10 @@
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C9" s="6">
         <v>420</v>
@@ -923,7 +923,7 @@
         <v>7</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C10" s="6">
         <v>380</v>
@@ -955,7 +955,7 @@
         <v>14</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C11" s="6">
         <v>76</v>
@@ -987,7 +987,7 @@
         <v>12</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C12" s="6">
         <v>445</v>
@@ -1019,7 +1019,7 @@
         <v>8</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C13" s="6">
         <v>542.70000000000005</v>
@@ -1048,10 +1048,10 @@
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C14" s="6">
         <v>527.29999999999995</v>
@@ -1083,7 +1083,7 @@
         <v>20</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C15" s="6">
         <v>606</v>
@@ -1115,7 +1115,7 @@
         <v>21</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C16" s="6">
         <v>366.6</v>
@@ -1144,10 +1144,10 @@
     </row>
     <row r="17" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C17" s="6">
         <v>74</v>
@@ -1179,7 +1179,7 @@
         <v>26</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C18" s="6">
         <v>76</v>
@@ -1211,7 +1211,7 @@
         <v>16</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C19" s="6">
         <v>50</v>
@@ -1240,10 +1240,10 @@
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C20" s="6">
         <v>89.6</v>
@@ -1272,10 +1272,10 @@
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C21" s="6">
         <v>89.6</v>
@@ -1307,7 +1307,7 @@
         <v>15</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C22" s="6">
         <v>483</v>
@@ -1339,7 +1339,7 @@
         <v>11</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C23" s="6">
         <v>69</v>
@@ -1371,7 +1371,7 @@
         <v>9</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C24" s="6">
         <v>100</v>
@@ -1403,7 +1403,7 @@
         <v>10</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C25" s="6">
         <v>74</v>
@@ -1435,7 +1435,7 @@
         <v>13</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C26" s="6">
         <v>1062.0999999999999</v>
@@ -1467,7 +1467,7 @@
         <v>19</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C27" s="6">
         <v>420</v>
@@ -1499,7 +1499,7 @@
         <v>73</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C28" s="6">
         <v>628.29999999999995</v>
@@ -1528,10 +1528,10 @@
     </row>
     <row r="29" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C29" s="6">
         <v>148</v>
@@ -1563,7 +1563,7 @@
         <v>22</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C30" s="6">
         <v>2100</v>
@@ -1592,10 +1592,10 @@
     </row>
     <row r="31" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C31" s="6">
         <v>700</v>
@@ -1627,7 +1627,7 @@
         <v>18</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C32" s="6">
         <v>70</v>
@@ -1659,7 +1659,7 @@
         <v>17</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C33" s="6">
         <v>170</v>
@@ -1803,7 +1803,7 @@
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A39" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B39" s="5"/>
       <c r="C39">
@@ -1824,7 +1824,7 @@
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A40" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B40" s="5"/>
       <c r="C40">
@@ -1873,22 +1873,22 @@
         <v>67</v>
       </c>
       <c r="C43" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="D43" s="6" t="s">
         <v>118</v>
       </c>
-      <c r="D43" s="6" t="s">
+      <c r="E43" s="6" t="s">
         <v>119</v>
       </c>
-      <c r="E43" s="6" t="s">
+      <c r="F43" s="6" t="s">
         <v>120</v>
       </c>
-      <c r="F43" s="6" t="s">
-        <v>121</v>
-      </c>
       <c r="G43" s="6" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H43" s="5" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.3">
@@ -1922,7 +1922,7 @@
         <v>31</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C46" s="1"/>
       <c r="D46" s="1"/>
@@ -2095,7 +2095,7 @@
         <v>45</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C60" s="1"/>
       <c r="D60" s="1"/>
@@ -2169,7 +2169,7 @@
         <v>51</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C66" s="1"/>
       <c r="D66" s="1"/>
@@ -2182,7 +2182,7 @@
         <v>52</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C67" s="1"/>
       <c r="D67" s="1"/>
@@ -2349,7 +2349,7 @@
         <v>65</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>76</v>
+        <v>128</v>
       </c>
       <c r="C80" s="1"/>
       <c r="D80" s="1"/>

--- a/data/gravel/Mason ISO 2025.xlsx
+++ b/data/gravel/Mason ISO 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10921"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7AC416B-A873-C343-A44A-DAAFCBCD3A20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D54E0EFB-083D-2147-B23F-DBFD6F59EE44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3060" yWindow="500" windowWidth="25740" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="130">
   <si>
     <t>brand</t>
   </si>
@@ -420,6 +420,9 @@
   </si>
   <si>
     <t>GBP</t>
+  </si>
+  <si>
+    <t>https://masoncycles.cc/images/000/003/089/medium/ISO2_FY_Side_GX_Web-InSitu.jpg?1740566379</t>
   </si>
 </sst>
 </file>
@@ -842,6 +845,11 @@
         <v>123</v>
       </c>
     </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="B6" t="s">
+        <v>129</v>
+      </c>
+    </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>5</v>

--- a/data/gravel/Mason ISO 2025.xlsx
+++ b/data/gravel/Mason ISO 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D54E0EFB-083D-2147-B23F-DBFD6F59EE44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45380C2D-0B04-2845-8D49-1CF1B9F8611D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3060" yWindow="500" windowWidth="25740" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="132">
   <si>
     <t>brand</t>
   </si>
@@ -423,6 +423,12 @@
   </si>
   <si>
     <t>https://masoncycles.cc/images/000/003/089/medium/ISO2_FY_Side_GX_Web-InSitu.jpg?1740566379</t>
+  </si>
+  <si>
+    <t>location</t>
+  </si>
+  <si>
+    <t>Lancing, West Sussex, United Kingdom</t>
   </si>
 </sst>
 </file>
@@ -799,7 +805,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P80"/>
+  <dimension ref="A1:P81"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -2364,6 +2370,14 @@
       <c r="E80" s="1"/>
       <c r="F80" s="1"/>
       <c r="G80" s="1"/>
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A81" t="s">
+        <v>130</v>
+      </c>
+      <c r="B81" t="s">
+        <v>131</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="8">

--- a/data/gravel/Mason ISO 2025.xlsx
+++ b/data/gravel/Mason ISO 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45380C2D-0B04-2845-8D49-1CF1B9F8611D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2614A181-866A-014C-ABB7-92D5660364CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3060" yWindow="500" windowWidth="25740" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="138">
   <si>
     <t>brand</t>
   </si>
@@ -429,6 +429,24 @@
   </si>
   <si>
     <t>Lancing, West Sussex, United Kingdom</t>
+  </si>
+  <si>
+    <t>head_tube_d</t>
+  </si>
+  <si>
+    <t>headset_upper</t>
+  </si>
+  <si>
+    <t>headset_lower</t>
+  </si>
+  <si>
+    <t>fork_steerer</t>
+  </si>
+  <si>
+    <t>fork_steerer_d</t>
+  </si>
+  <si>
+    <t>fork_material</t>
   </si>
 </sst>
 </file>
@@ -805,7 +823,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P81"/>
+  <dimension ref="A1:P87"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -2069,11 +2087,9 @@
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A57" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B57" s="1" t="s">
-        <v>74</v>
-      </c>
+        <v>132</v>
+      </c>
+      <c r="B57" s="1"/>
       <c r="C57" s="1"/>
       <c r="D57" s="1"/>
       <c r="E57" s="1"/>
@@ -2082,7 +2098,7 @@
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A58" s="1" t="s">
-        <v>43</v>
+        <v>133</v>
       </c>
       <c r="B58" s="1"/>
       <c r="C58" s="1"/>
@@ -2093,11 +2109,9 @@
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A59" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B59" s="1">
-        <v>31.6</v>
-      </c>
+        <v>134</v>
+      </c>
+      <c r="B59" s="1"/>
       <c r="C59" s="1"/>
       <c r="D59" s="1"/>
       <c r="E59" s="1"/>
@@ -2106,11 +2120,9 @@
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A60" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="B60" s="1" t="s">
-        <v>124</v>
-      </c>
+        <v>135</v>
+      </c>
+      <c r="B60" s="1"/>
       <c r="C60" s="1"/>
       <c r="D60" s="1"/>
       <c r="E60" s="1"/>
@@ -2119,11 +2131,9 @@
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A61" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="B61" s="1">
-        <v>36</v>
-      </c>
+        <v>136</v>
+      </c>
+      <c r="B61" s="1"/>
       <c r="C61" s="1"/>
       <c r="D61" s="1"/>
       <c r="E61" s="1"/>
@@ -2132,7 +2142,7 @@
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A62" s="1" t="s">
-        <v>47</v>
+        <v>137</v>
       </c>
       <c r="B62" s="1"/>
       <c r="C62" s="1"/>
@@ -2143,10 +2153,10 @@
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A63" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="B63" s="1">
-        <v>180</v>
+        <v>42</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>74</v>
       </c>
       <c r="C63" s="1"/>
       <c r="D63" s="1"/>
@@ -2156,11 +2166,9 @@
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A64" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="B64" s="1">
-        <v>160</v>
-      </c>
+        <v>43</v>
+      </c>
+      <c r="B64" s="1"/>
       <c r="C64" s="1"/>
       <c r="D64" s="1"/>
       <c r="E64" s="1"/>
@@ -2169,9 +2177,11 @@
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A65" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="B65" s="1"/>
+        <v>44</v>
+      </c>
+      <c r="B65" s="1">
+        <v>31.6</v>
+      </c>
       <c r="C65" s="1"/>
       <c r="D65" s="1"/>
       <c r="E65" s="1"/>
@@ -2180,10 +2190,10 @@
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A66" s="1" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>110</v>
+        <v>124</v>
       </c>
       <c r="C66" s="1"/>
       <c r="D66" s="1"/>
@@ -2193,10 +2203,10 @@
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A67" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="B67" s="1" t="s">
-        <v>110</v>
+        <v>46</v>
+      </c>
+      <c r="B67" s="1">
+        <v>36</v>
       </c>
       <c r="C67" s="1"/>
       <c r="D67" s="1"/>
@@ -2206,11 +2216,9 @@
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A68" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="B68" s="1" t="s">
-        <v>72</v>
-      </c>
+        <v>47</v>
+      </c>
+      <c r="B68" s="1"/>
       <c r="C68" s="1"/>
       <c r="D68" s="1"/>
       <c r="E68" s="1"/>
@@ -2219,9 +2227,11 @@
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A69" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="B69" s="1"/>
+        <v>48</v>
+      </c>
+      <c r="B69" s="1">
+        <v>180</v>
+      </c>
       <c r="C69" s="1"/>
       <c r="D69" s="1"/>
       <c r="E69" s="1"/>
@@ -2230,10 +2240,10 @@
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A70" s="1" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="B70" s="1">
-        <v>2</v>
+        <v>160</v>
       </c>
       <c r="C70" s="1"/>
       <c r="D70" s="1"/>
@@ -2243,11 +2253,9 @@
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A71" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="B71" s="1">
-        <v>1</v>
-      </c>
+        <v>50</v>
+      </c>
+      <c r="B71" s="1"/>
       <c r="C71" s="1"/>
       <c r="D71" s="1"/>
       <c r="E71" s="1"/>
@@ -2256,10 +2264,10 @@
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A72" s="1" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>72</v>
+        <v>110</v>
       </c>
       <c r="C72" s="1"/>
       <c r="D72" s="1"/>
@@ -2269,10 +2277,10 @@
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A73" s="1" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>72</v>
+        <v>110</v>
       </c>
       <c r="C73" s="1"/>
       <c r="D73" s="1"/>
@@ -2282,7 +2290,7 @@
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A74" s="1" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="B74" s="1" t="s">
         <v>72</v>
@@ -2295,11 +2303,9 @@
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A75" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="B75" s="1" t="s">
-        <v>72</v>
-      </c>
+        <v>54</v>
+      </c>
+      <c r="B75" s="1"/>
       <c r="C75" s="1"/>
       <c r="D75" s="1"/>
       <c r="E75" s="1"/>
@@ -2308,10 +2314,10 @@
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A76" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="B76" s="1" t="s">
-        <v>72</v>
+        <v>55</v>
+      </c>
+      <c r="B76" s="1">
+        <v>2</v>
       </c>
       <c r="C76" s="1"/>
       <c r="D76" s="1"/>
@@ -2321,10 +2327,10 @@
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A77" s="1" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="B77" s="1">
-        <v>1795</v>
+        <v>1</v>
       </c>
       <c r="C77" s="1"/>
       <c r="D77" s="1"/>
@@ -2334,10 +2340,10 @@
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A78" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="B78" s="1">
-        <v>3000</v>
+        <v>57</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>72</v>
       </c>
       <c r="C78" s="1"/>
       <c r="D78" s="1"/>
@@ -2347,7 +2353,7 @@
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A79" s="1" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="B79" s="1" t="s">
         <v>72</v>
@@ -2360,10 +2366,10 @@
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A80" s="1" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>128</v>
+        <v>72</v>
       </c>
       <c r="C80" s="1"/>
       <c r="D80" s="1"/>
@@ -2371,11 +2377,89 @@
       <c r="F80" s="1"/>
       <c r="G80" s="1"/>
     </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A81" t="s">
+    <row r="81" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A81" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B81" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="C81" s="1"/>
+      <c r="D81" s="1"/>
+      <c r="E81" s="1"/>
+      <c r="F81" s="1"/>
+      <c r="G81" s="1"/>
+    </row>
+    <row r="82" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A82" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B82" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="C82" s="1"/>
+      <c r="D82" s="1"/>
+      <c r="E82" s="1"/>
+      <c r="F82" s="1"/>
+      <c r="G82" s="1"/>
+    </row>
+    <row r="83" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A83" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B83" s="1">
+        <v>1795</v>
+      </c>
+      <c r="C83" s="1"/>
+      <c r="D83" s="1"/>
+      <c r="E83" s="1"/>
+      <c r="F83" s="1"/>
+      <c r="G83" s="1"/>
+    </row>
+    <row r="84" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A84" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B84" s="1">
+        <v>3000</v>
+      </c>
+      <c r="C84" s="1"/>
+      <c r="D84" s="1"/>
+      <c r="E84" s="1"/>
+      <c r="F84" s="1"/>
+      <c r="G84" s="1"/>
+    </row>
+    <row r="85" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A85" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B85" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="C85" s="1"/>
+      <c r="D85" s="1"/>
+      <c r="E85" s="1"/>
+      <c r="F85" s="1"/>
+      <c r="G85" s="1"/>
+    </row>
+    <row r="86" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A86" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B86" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="C86" s="1"/>
+      <c r="D86" s="1"/>
+      <c r="E86" s="1"/>
+      <c r="F86" s="1"/>
+      <c r="G86" s="1"/>
+    </row>
+    <row r="87" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A87" t="s">
         <v>130</v>
       </c>
-      <c r="B81" t="s">
+      <c r="B87" t="s">
         <v>131</v>
       </c>
     </row>

--- a/data/gravel/Mason ISO 2025.xlsx
+++ b/data/gravel/Mason ISO 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11109"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2614A181-866A-014C-ABB7-92D5660364CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A113FB93-56E9-1C4B-AA34-CB834B6A1C93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3060" yWindow="500" windowWidth="25740" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -453,7 +453,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="14"/>
       <color rgb="FF000000"/>
@@ -496,6 +496,21 @@
       <name val="Helvetica Neue"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="14"/>
+      <color rgb="FFFD4722"/>
+      <name val="Futura Medium"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color rgb="FF020203"/>
+      <name val="Futura Medium"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color rgb="FF000000"/>
+      <name val="Futura Medium"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -517,7 +532,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -527,6 +542,9 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -922,22 +940,22 @@
       <c r="A9" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="9" t="s">
         <v>79</v>
       </c>
-      <c r="C9" s="6">
+      <c r="C9" s="10">
         <v>420</v>
       </c>
-      <c r="D9" s="6">
+      <c r="D9" s="10">
         <v>460</v>
       </c>
-      <c r="E9" s="6">
+      <c r="E9" s="10">
         <v>500</v>
       </c>
-      <c r="F9" s="6">
+      <c r="F9" s="10">
         <v>540</v>
       </c>
-      <c r="G9" s="6">
+      <c r="G9" s="10">
         <v>580</v>
       </c>
       <c r="H9" s="5"/>
@@ -954,22 +972,22 @@
       <c r="A10" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="9" t="s">
         <v>80</v>
       </c>
-      <c r="C10" s="6">
+      <c r="C10" s="10">
         <v>380</v>
       </c>
-      <c r="D10" s="6">
+      <c r="D10" s="10">
         <v>415</v>
       </c>
-      <c r="E10" s="6">
+      <c r="E10" s="10">
         <v>445</v>
       </c>
-      <c r="F10" s="6">
+      <c r="F10" s="10">
         <v>490</v>
       </c>
-      <c r="G10" s="6">
+      <c r="G10" s="10">
         <v>530</v>
       </c>
       <c r="H10" s="5"/>
@@ -986,22 +1004,22 @@
       <c r="A11" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="C11" s="6">
+      <c r="C11" s="10">
         <v>76</v>
       </c>
-      <c r="D11" s="6">
+      <c r="D11" s="10">
         <v>75</v>
       </c>
-      <c r="E11" s="6">
+      <c r="E11" s="10">
         <v>75</v>
       </c>
-      <c r="F11" s="6">
+      <c r="F11" s="10">
         <v>75</v>
       </c>
-      <c r="G11" s="6">
+      <c r="G11" s="10">
         <v>73</v>
       </c>
       <c r="H11" s="5"/>
@@ -1018,22 +1036,22 @@
       <c r="A12" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B12" s="9" t="s">
         <v>82</v>
       </c>
-      <c r="C12" s="6">
+      <c r="C12" s="10">
         <v>445</v>
       </c>
-      <c r="D12" s="6">
+      <c r="D12" s="10">
         <v>445</v>
       </c>
-      <c r="E12" s="6">
+      <c r="E12" s="10">
         <v>445</v>
       </c>
-      <c r="F12" s="6">
+      <c r="F12" s="10">
         <v>445</v>
       </c>
-      <c r="G12" s="6">
+      <c r="G12" s="10">
         <v>445</v>
       </c>
       <c r="H12" s="5"/>
@@ -1050,22 +1068,22 @@
       <c r="A13" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B13" s="9" t="s">
         <v>83</v>
       </c>
-      <c r="C13" s="6">
+      <c r="C13" s="10">
         <v>542.70000000000005</v>
       </c>
-      <c r="D13" s="6">
+      <c r="D13" s="10">
         <v>554.1</v>
       </c>
-      <c r="E13" s="6">
+      <c r="E13" s="10">
         <v>560.5</v>
       </c>
-      <c r="F13" s="6">
+      <c r="F13" s="10">
         <v>567.6</v>
       </c>
-      <c r="G13" s="6">
+      <c r="G13" s="10">
         <v>587</v>
       </c>
       <c r="H13" s="5"/>
@@ -1082,22 +1100,22 @@
       <c r="A14" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="B14" s="9" t="s">
         <v>84</v>
       </c>
-      <c r="C14" s="6">
+      <c r="C14" s="10">
         <v>527.29999999999995</v>
       </c>
-      <c r="D14" s="6">
+      <c r="D14" s="10">
         <v>534.70000000000005</v>
       </c>
-      <c r="E14" s="6">
+      <c r="E14" s="10">
         <v>539</v>
       </c>
-      <c r="F14" s="6">
+      <c r="F14" s="10">
         <v>545.70000000000005</v>
       </c>
-      <c r="G14" s="6">
+      <c r="G14" s="10">
         <v>565.20000000000005</v>
       </c>
       <c r="H14" s="5"/>
@@ -1114,22 +1132,22 @@
       <c r="A15" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="B15" s="9" t="s">
         <v>85</v>
       </c>
-      <c r="C15" s="6">
+      <c r="C15" s="10">
         <v>606</v>
       </c>
-      <c r="D15" s="6">
+      <c r="D15" s="10">
         <v>614.4</v>
       </c>
-      <c r="E15" s="6">
+      <c r="E15" s="10">
         <v>623.79999999999995</v>
       </c>
-      <c r="F15" s="6">
+      <c r="F15" s="10">
         <v>633.1</v>
       </c>
-      <c r="G15" s="6">
+      <c r="G15" s="10">
         <v>654.5</v>
       </c>
       <c r="H15" s="5"/>
@@ -1146,22 +1164,22 @@
       <c r="A16" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B16" s="5" t="s">
+      <c r="B16" s="9" t="s">
         <v>86</v>
       </c>
-      <c r="C16" s="6">
+      <c r="C16" s="10">
         <v>366.6</v>
       </c>
-      <c r="D16" s="6">
+      <c r="D16" s="10">
         <v>375.7</v>
       </c>
-      <c r="E16" s="6">
+      <c r="E16" s="10">
         <v>379.4</v>
       </c>
-      <c r="F16" s="6">
+      <c r="F16" s="10">
         <v>384</v>
       </c>
-      <c r="G16" s="6">
+      <c r="G16" s="10">
         <v>397.4</v>
       </c>
       <c r="H16" s="5"/>
@@ -1178,30 +1196,45 @@
       <c r="A17" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="B17" s="5" t="s">
+      <c r="B17" s="9" t="s">
         <v>113</v>
       </c>
-      <c r="C17" s="6">
+      <c r="C17" s="10">
+        <f>I17*10</f>
+        <v>740</v>
+      </c>
+      <c r="D17" s="10">
+        <f t="shared" ref="D17:G17" si="0">J17*10</f>
+        <v>765</v>
+      </c>
+      <c r="E17" s="10">
+        <f t="shared" si="0"/>
+        <v>790</v>
+      </c>
+      <c r="F17" s="10">
+        <f t="shared" si="0"/>
+        <v>825</v>
+      </c>
+      <c r="G17" s="10">
+        <f t="shared" si="0"/>
+        <v>865</v>
+      </c>
+      <c r="H17" s="5"/>
+      <c r="I17" s="10">
         <v>74</v>
       </c>
-      <c r="D17" s="6">
+      <c r="J17" s="10">
         <v>76.5</v>
       </c>
-      <c r="E17" s="6">
+      <c r="K17" s="10">
         <v>79</v>
       </c>
-      <c r="F17" s="6">
+      <c r="L17" s="10">
         <v>82.5</v>
       </c>
-      <c r="G17" s="6">
+      <c r="M17" s="10">
         <v>86.5</v>
       </c>
-      <c r="H17" s="5"/>
-      <c r="I17" s="6"/>
-      <c r="J17" s="6"/>
-      <c r="K17" s="6"/>
-      <c r="L17" s="6"/>
-      <c r="M17" s="6"/>
       <c r="N17" s="6"/>
       <c r="O17" s="6"/>
       <c r="P17" s="6"/>
@@ -1210,30 +1243,45 @@
       <c r="A18" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B18" s="5" t="s">
+      <c r="B18" s="9" t="s">
         <v>114</v>
       </c>
-      <c r="C18" s="6">
+      <c r="C18" s="10">
+        <f>I18*10</f>
+        <v>760</v>
+      </c>
+      <c r="D18" s="10">
+        <f t="shared" ref="D18" si="1">J18*10</f>
+        <v>785</v>
+      </c>
+      <c r="E18" s="10">
+        <f t="shared" ref="E18" si="2">K18*10</f>
+        <v>810</v>
+      </c>
+      <c r="F18" s="10">
+        <f t="shared" ref="F18" si="3">L18*10</f>
+        <v>845</v>
+      </c>
+      <c r="G18" s="10">
+        <f t="shared" ref="G18" si="4">M18*10</f>
+        <v>885</v>
+      </c>
+      <c r="H18" s="5"/>
+      <c r="I18" s="10">
         <v>76</v>
       </c>
-      <c r="D18" s="6">
+      <c r="J18" s="10">
         <v>78.5</v>
       </c>
-      <c r="E18" s="6">
+      <c r="K18" s="10">
         <v>81</v>
       </c>
-      <c r="F18" s="6">
+      <c r="L18" s="10">
         <v>84.5</v>
       </c>
-      <c r="G18" s="6">
+      <c r="M18" s="10">
         <v>88.5</v>
       </c>
-      <c r="H18" s="5"/>
-      <c r="I18" s="6"/>
-      <c r="J18" s="6"/>
-      <c r="K18" s="6"/>
-      <c r="L18" s="6"/>
-      <c r="M18" s="6"/>
       <c r="N18" s="6"/>
       <c r="O18" s="6"/>
       <c r="P18" s="6"/>
@@ -1242,22 +1290,22 @@
       <c r="A19" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B19" s="5" t="s">
+      <c r="B19" s="9" t="s">
         <v>87</v>
       </c>
-      <c r="C19" s="6">
+      <c r="C19" s="10">
         <v>50</v>
       </c>
-      <c r="D19" s="6">
+      <c r="D19" s="10">
         <v>50</v>
       </c>
-      <c r="E19" s="6">
+      <c r="E19" s="10">
         <v>50</v>
       </c>
-      <c r="F19" s="6">
+      <c r="F19" s="10">
         <v>50</v>
       </c>
-      <c r="G19" s="6">
+      <c r="G19" s="10">
         <v>50</v>
       </c>
       <c r="H19" s="5"/>
@@ -1274,22 +1322,22 @@
       <c r="A20" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="B20" s="5" t="s">
+      <c r="B20" s="9" t="s">
         <v>88</v>
       </c>
-      <c r="C20" s="6">
+      <c r="C20" s="10">
         <v>89.6</v>
       </c>
-      <c r="D20" s="6">
+      <c r="D20" s="10">
         <v>89.6</v>
       </c>
-      <c r="E20" s="6">
+      <c r="E20" s="10">
         <v>89.6</v>
       </c>
-      <c r="F20" s="6">
+      <c r="F20" s="10">
         <v>89.6</v>
       </c>
-      <c r="G20" s="6">
+      <c r="G20" s="10">
         <v>82.6</v>
       </c>
       <c r="H20" s="5"/>
@@ -1306,22 +1354,22 @@
       <c r="A21" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="B21" s="5" t="s">
+      <c r="B21" s="9" t="s">
         <v>115</v>
       </c>
-      <c r="C21" s="6">
+      <c r="C21" s="10">
         <v>89.6</v>
       </c>
-      <c r="D21" s="6">
+      <c r="D21" s="10">
         <v>89.6</v>
       </c>
-      <c r="E21" s="6">
+      <c r="E21" s="10">
         <v>89.6</v>
       </c>
-      <c r="F21" s="6">
+      <c r="F21" s="10">
         <v>89.6</v>
       </c>
-      <c r="G21" s="6">
+      <c r="G21" s="10">
         <v>82.6</v>
       </c>
       <c r="H21" s="5"/>
@@ -1338,22 +1386,22 @@
       <c r="A22" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B22" s="5" t="s">
+      <c r="B22" s="9" t="s">
         <v>89</v>
       </c>
-      <c r="C22" s="6">
+      <c r="C22" s="10">
         <v>483</v>
       </c>
-      <c r="D22" s="6">
+      <c r="D22" s="10">
         <v>483</v>
       </c>
-      <c r="E22" s="6">
+      <c r="E22" s="10">
         <v>483</v>
       </c>
-      <c r="F22" s="6">
+      <c r="F22" s="10">
         <v>483</v>
       </c>
-      <c r="G22" s="6">
+      <c r="G22" s="10">
         <v>483</v>
       </c>
       <c r="H22" s="7"/>
@@ -1370,22 +1418,22 @@
       <c r="A23" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B23" s="5" t="s">
+      <c r="B23" s="9" t="s">
         <v>90</v>
       </c>
-      <c r="C23" s="6">
+      <c r="C23" s="10">
         <v>69</v>
       </c>
-      <c r="D23" s="6">
+      <c r="D23" s="10">
         <v>69</v>
       </c>
-      <c r="E23" s="6">
+      <c r="E23" s="10">
         <v>69</v>
       </c>
-      <c r="F23" s="6">
+      <c r="F23" s="10">
         <v>69</v>
       </c>
-      <c r="G23" s="6">
+      <c r="G23" s="10">
         <v>70</v>
       </c>
       <c r="H23" s="5"/>
@@ -1402,22 +1450,22 @@
       <c r="A24" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B24" s="5" t="s">
+      <c r="B24" s="9" t="s">
         <v>91</v>
       </c>
-      <c r="C24" s="6">
+      <c r="C24" s="10">
         <v>100</v>
       </c>
-      <c r="D24" s="6">
+      <c r="D24" s="10">
         <v>110</v>
       </c>
-      <c r="E24" s="6">
+      <c r="E24" s="10">
         <v>120</v>
       </c>
-      <c r="F24" s="6">
+      <c r="F24" s="10">
         <v>130</v>
       </c>
-      <c r="G24" s="6">
+      <c r="G24" s="10">
         <v>150</v>
       </c>
       <c r="H24" s="5"/>
@@ -1434,22 +1482,22 @@
       <c r="A25" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B25" s="5" t="s">
+      <c r="B25" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="C25" s="6">
+      <c r="C25" s="10">
         <v>74</v>
       </c>
-      <c r="D25" s="6">
+      <c r="D25" s="10">
         <v>74</v>
       </c>
-      <c r="E25" s="6">
+      <c r="E25" s="10">
         <v>74</v>
       </c>
-      <c r="F25" s="6">
+      <c r="F25" s="10">
         <v>74</v>
       </c>
-      <c r="G25" s="6">
+      <c r="G25" s="10">
         <v>74</v>
       </c>
       <c r="H25" s="5"/>
@@ -1466,22 +1514,22 @@
       <c r="A26" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B26" s="5" t="s">
+      <c r="B26" s="9" t="s">
         <v>93</v>
       </c>
-      <c r="C26" s="6">
+      <c r="C26" s="10">
         <v>1062.0999999999999</v>
       </c>
-      <c r="D26" s="6">
+      <c r="D26" s="10">
         <v>1075</v>
       </c>
-      <c r="E26" s="6">
+      <c r="E26" s="10">
         <v>1082.3</v>
       </c>
-      <c r="F26" s="6">
+      <c r="F26" s="10">
         <v>1090.2</v>
       </c>
-      <c r="G26" s="6">
+      <c r="G26" s="10">
         <v>1101.3</v>
       </c>
       <c r="H26" s="5"/>
@@ -1498,22 +1546,22 @@
       <c r="A27" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B27" s="5" t="s">
+      <c r="B27" s="9" t="s">
         <v>94</v>
       </c>
-      <c r="C27" s="6">
+      <c r="C27" s="10">
         <v>420</v>
       </c>
-      <c r="D27" s="6">
+      <c r="D27" s="10">
         <v>440</v>
       </c>
-      <c r="E27" s="6">
+      <c r="E27" s="10">
         <v>460</v>
       </c>
-      <c r="F27" s="6">
+      <c r="F27" s="10">
         <v>460</v>
       </c>
-      <c r="G27" s="6">
+      <c r="G27" s="10">
         <v>480</v>
       </c>
       <c r="H27" s="5"/>
@@ -1530,22 +1578,22 @@
       <c r="A28" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="B28" s="5" t="s">
+      <c r="B28" s="9" t="s">
         <v>95</v>
       </c>
-      <c r="C28" s="6">
+      <c r="C28" s="10">
         <v>628.29999999999995</v>
       </c>
-      <c r="D28" s="6">
+      <c r="D28" s="10">
         <v>640.70000000000005</v>
       </c>
-      <c r="E28" s="6">
+      <c r="E28" s="10">
         <v>648</v>
       </c>
-      <c r="F28" s="6">
+      <c r="F28" s="10">
         <v>656</v>
       </c>
-      <c r="G28" s="6">
+      <c r="G28" s="10">
         <v>666.3</v>
       </c>
       <c r="H28" s="5"/>
@@ -1562,22 +1610,22 @@
       <c r="A29" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="B29" s="5" t="s">
+      <c r="B29" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="C29" s="6">
+      <c r="C29" s="10">
         <v>148</v>
       </c>
-      <c r="D29" s="6">
+      <c r="D29" s="10">
         <v>148</v>
       </c>
-      <c r="E29" s="6">
+      <c r="E29" s="10">
         <v>148</v>
       </c>
-      <c r="F29" s="6">
+      <c r="F29" s="10">
         <v>148</v>
       </c>
-      <c r="G29" s="6">
+      <c r="G29" s="10">
         <v>148</v>
       </c>
       <c r="H29" s="5"/>
@@ -1594,22 +1642,22 @@
       <c r="A30" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B30" s="5" t="s">
+      <c r="B30" s="9" t="s">
         <v>107</v>
       </c>
-      <c r="C30" s="6">
+      <c r="C30" s="10">
         <v>2100</v>
       </c>
-      <c r="D30" s="6">
+      <c r="D30" s="10">
         <v>2180</v>
       </c>
-      <c r="E30" s="6">
+      <c r="E30" s="10">
         <v>2260</v>
       </c>
-      <c r="F30" s="6">
+      <c r="F30" s="10">
         <v>2400</v>
       </c>
-      <c r="G30" s="6">
+      <c r="G30" s="10">
         <v>2480</v>
       </c>
       <c r="H30" s="5"/>
@@ -1626,22 +1674,22 @@
       <c r="A31" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="B31" s="5" t="s">
+      <c r="B31" s="9" t="s">
         <v>116</v>
       </c>
-      <c r="C31" s="6">
+      <c r="C31" s="10">
         <v>700</v>
       </c>
-      <c r="D31" s="6">
+      <c r="D31" s="10">
         <v>700</v>
       </c>
-      <c r="E31" s="6">
+      <c r="E31" s="10">
         <v>700</v>
       </c>
-      <c r="F31" s="6">
+      <c r="F31" s="10">
         <v>700</v>
       </c>
-      <c r="G31" s="6">
+      <c r="G31" s="10">
         <v>700</v>
       </c>
       <c r="H31" s="5"/>
@@ -1658,22 +1706,22 @@
       <c r="A32" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B32" s="5" t="s">
+      <c r="B32" s="9" t="s">
         <v>99</v>
       </c>
-      <c r="C32" s="6">
+      <c r="C32" s="10">
         <v>70</v>
       </c>
-      <c r="D32" s="6">
+      <c r="D32" s="10">
         <v>70</v>
       </c>
-      <c r="E32" s="6">
+      <c r="E32" s="10">
         <v>80</v>
       </c>
-      <c r="F32" s="6">
+      <c r="F32" s="10">
         <v>90</v>
       </c>
-      <c r="G32" s="6">
+      <c r="G32" s="10">
         <v>100</v>
       </c>
       <c r="H32" s="5"/>
@@ -1690,22 +1738,22 @@
       <c r="A33" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B33" s="5" t="s">
+      <c r="B33" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="C33" s="6">
+      <c r="C33" s="10">
         <v>170</v>
       </c>
-      <c r="D33" s="6">
+      <c r="D33" s="10">
         <v>170</v>
       </c>
-      <c r="E33" s="6">
+      <c r="E33" s="10">
         <v>170</v>
       </c>
-      <c r="F33" s="6">
+      <c r="F33" s="10">
         <v>170</v>
       </c>
-      <c r="G33" s="6">
+      <c r="G33" s="10">
         <v>175</v>
       </c>
     </row>
@@ -1713,19 +1761,20 @@
       <c r="A34" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="C34" s="6">
+      <c r="B34" s="11"/>
+      <c r="C34" s="10">
         <v>700</v>
       </c>
-      <c r="D34" s="6">
+      <c r="D34" s="10">
         <v>700</v>
       </c>
-      <c r="E34" s="6">
+      <c r="E34" s="10">
         <v>700</v>
       </c>
-      <c r="F34" s="6">
+      <c r="F34" s="10">
         <v>700</v>
       </c>
-      <c r="G34" s="6">
+      <c r="G34" s="10">
         <v>700</v>
       </c>
     </row>
@@ -1733,25 +1782,25 @@
       <c r="A35" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B35" s="5"/>
-      <c r="C35" s="6">
+      <c r="B35" s="9"/>
+      <c r="C35" s="10">
         <f>2.4*25.4</f>
         <v>60.959999999999994</v>
       </c>
-      <c r="D35" s="6">
-        <f t="shared" ref="D35:G35" si="0">2.4*25.4</f>
+      <c r="D35" s="10">
+        <f t="shared" ref="D35:G35" si="5">2.4*25.4</f>
         <v>60.959999999999994</v>
       </c>
-      <c r="E35" s="6">
-        <f t="shared" si="0"/>
+      <c r="E35" s="10">
+        <f t="shared" si="5"/>
         <v>60.959999999999994</v>
       </c>
-      <c r="F35" s="6">
-        <f t="shared" si="0"/>
+      <c r="F35" s="10">
+        <f t="shared" si="5"/>
         <v>60.959999999999994</v>
       </c>
-      <c r="G35" s="6">
-        <f t="shared" si="0"/>
+      <c r="G35" s="10">
+        <f t="shared" si="5"/>
         <v>60.959999999999994</v>
       </c>
     </row>
@@ -1759,25 +1808,25 @@
       <c r="A36" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="B36" s="5"/>
-      <c r="C36" s="1">
+      <c r="B36" s="9"/>
+      <c r="C36" s="11">
         <f>2.6*24.5</f>
         <v>63.7</v>
       </c>
-      <c r="D36" s="1">
-        <f t="shared" ref="D36:G36" si="1">2.6*24.5</f>
+      <c r="D36" s="11">
+        <f t="shared" ref="D36:G36" si="6">2.6*24.5</f>
         <v>63.7</v>
       </c>
-      <c r="E36" s="1">
-        <f t="shared" si="1"/>
+      <c r="E36" s="11">
+        <f t="shared" si="6"/>
         <v>63.7</v>
       </c>
-      <c r="F36" s="1">
-        <f t="shared" si="1"/>
+      <c r="F36" s="11">
+        <f t="shared" si="6"/>
         <v>63.7</v>
       </c>
-      <c r="G36" s="1">
-        <f t="shared" si="1"/>
+      <c r="G36" s="11">
+        <f t="shared" si="6"/>
         <v>63.7</v>
       </c>
     </row>
@@ -1785,25 +1834,25 @@
       <c r="A37" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B37" s="5"/>
-      <c r="C37" s="1">
+      <c r="B37" s="9"/>
+      <c r="C37" s="11">
         <f>C39</f>
         <v>151</v>
       </c>
-      <c r="D37" s="1">
+      <c r="D37" s="11">
         <f>AVERAGE(D39,C40)</f>
         <v>162.5</v>
       </c>
-      <c r="E37" s="1">
-        <f t="shared" ref="E37:G37" si="2">AVERAGE(E39,D40)</f>
+      <c r="E37" s="11">
+        <f t="shared" ref="E37:G37" si="7">AVERAGE(E39,D40)</f>
         <v>172</v>
       </c>
-      <c r="F37" s="1">
-        <f t="shared" si="2"/>
+      <c r="F37" s="11">
+        <f t="shared" si="7"/>
         <v>181.5</v>
       </c>
-      <c r="G37" s="1">
-        <f t="shared" si="2"/>
+      <c r="G37" s="11">
+        <f t="shared" si="7"/>
         <v>189</v>
       </c>
     </row>
@@ -1811,24 +1860,24 @@
       <c r="A38" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B38" s="5"/>
-      <c r="C38">
+      <c r="B38" s="9"/>
+      <c r="C38" s="11">
         <f>D37</f>
         <v>162.5</v>
       </c>
-      <c r="D38">
-        <f t="shared" ref="D38:F38" si="3">E37</f>
+      <c r="D38" s="11">
+        <f t="shared" ref="D38:F38" si="8">E37</f>
         <v>172</v>
       </c>
-      <c r="E38">
-        <f t="shared" si="3"/>
+      <c r="E38" s="11">
+        <f t="shared" si="8"/>
         <v>181.5</v>
       </c>
-      <c r="F38">
-        <f t="shared" si="3"/>
+      <c r="F38" s="11">
+        <f t="shared" si="8"/>
         <v>189</v>
       </c>
-      <c r="G38">
+      <c r="G38" s="11">
         <f>G40</f>
         <v>198</v>
       </c>
@@ -1837,20 +1886,20 @@
       <c r="A39" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="B39" s="5"/>
-      <c r="C39">
+      <c r="B39" s="9"/>
+      <c r="C39" s="11">
         <v>151</v>
       </c>
-      <c r="D39">
+      <c r="D39" s="11">
         <v>162</v>
       </c>
-      <c r="E39">
+      <c r="E39" s="11">
         <v>170</v>
       </c>
-      <c r="F39">
+      <c r="F39" s="11">
         <v>180</v>
       </c>
-      <c r="G39">
+      <c r="G39" s="11">
         <v>188</v>
       </c>
     </row>
@@ -1858,20 +1907,20 @@
       <c r="A40" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="B40" s="5"/>
-      <c r="C40">
+      <c r="B40" s="9"/>
+      <c r="C40" s="11">
         <v>163</v>
       </c>
-      <c r="D40">
+      <c r="D40" s="11">
         <v>174</v>
       </c>
-      <c r="E40">
+      <c r="E40" s="11">
         <v>183</v>
       </c>
-      <c r="F40">
+      <c r="F40" s="11">
         <v>190</v>
       </c>
-      <c r="G40">
+      <c r="G40" s="11">
         <v>198</v>
       </c>
     </row>

--- a/data/gravel/Mason ISO 2025.xlsx
+++ b/data/gravel/Mason ISO 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11109"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11122"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A113FB93-56E9-1C4B-AA34-CB834B6A1C93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{840DCDEF-7426-7C43-B19F-F232B00BD263}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3060" yWindow="500" windowWidth="25740" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="140">
   <si>
     <t>brand</t>
   </si>
@@ -413,9 +413,6 @@
     <t>ISO</t>
   </si>
   <si>
-    <t>a8:g40</t>
-  </si>
-  <si>
     <t>rear_axle_spec</t>
   </si>
   <si>
@@ -447,6 +444,15 @@
   </si>
   <si>
     <t>fork_material</t>
+  </si>
+  <si>
+    <t>fork_travel</t>
+  </si>
+  <si>
+    <t>fork_sag</t>
+  </si>
+  <si>
+    <t>a8:g42</t>
   </si>
 </sst>
 </file>
@@ -541,10 +547,10 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -841,7 +847,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P87"/>
+  <dimension ref="A1:P89"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -889,7 +895,7 @@
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.3">
@@ -897,7 +903,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>126</v>
+        <v>139</v>
       </c>
       <c r="C7" s="1"/>
       <c r="D7" s="1"/>
@@ -940,22 +946,22 @@
       <c r="A9" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="B9" s="9" t="s">
+      <c r="B9" s="8" t="s">
         <v>79</v>
       </c>
-      <c r="C9" s="10">
+      <c r="C9" s="9">
         <v>420</v>
       </c>
-      <c r="D9" s="10">
+      <c r="D9" s="9">
         <v>460</v>
       </c>
-      <c r="E9" s="10">
+      <c r="E9" s="9">
         <v>500</v>
       </c>
-      <c r="F9" s="10">
+      <c r="F9" s="9">
         <v>540</v>
       </c>
-      <c r="G9" s="10">
+      <c r="G9" s="9">
         <v>580</v>
       </c>
       <c r="H9" s="5"/>
@@ -972,22 +978,22 @@
       <c r="A10" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B10" s="9" t="s">
+      <c r="B10" s="8" t="s">
         <v>80</v>
       </c>
-      <c r="C10" s="10">
+      <c r="C10" s="9">
         <v>380</v>
       </c>
-      <c r="D10" s="10">
+      <c r="D10" s="9">
         <v>415</v>
       </c>
-      <c r="E10" s="10">
+      <c r="E10" s="9">
         <v>445</v>
       </c>
-      <c r="F10" s="10">
+      <c r="F10" s="9">
         <v>490</v>
       </c>
-      <c r="G10" s="10">
+      <c r="G10" s="9">
         <v>530</v>
       </c>
       <c r="H10" s="5"/>
@@ -1004,22 +1010,22 @@
       <c r="A11" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B11" s="9" t="s">
+      <c r="B11" s="8" t="s">
         <v>81</v>
       </c>
-      <c r="C11" s="10">
+      <c r="C11" s="9">
         <v>76</v>
       </c>
-      <c r="D11" s="10">
+      <c r="D11" s="9">
         <v>75</v>
       </c>
-      <c r="E11" s="10">
+      <c r="E11" s="9">
         <v>75</v>
       </c>
-      <c r="F11" s="10">
+      <c r="F11" s="9">
         <v>75</v>
       </c>
-      <c r="G11" s="10">
+      <c r="G11" s="9">
         <v>73</v>
       </c>
       <c r="H11" s="5"/>
@@ -1036,22 +1042,22 @@
       <c r="A12" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B12" s="9" t="s">
+      <c r="B12" s="8" t="s">
         <v>82</v>
       </c>
-      <c r="C12" s="10">
+      <c r="C12" s="9">
         <v>445</v>
       </c>
-      <c r="D12" s="10">
+      <c r="D12" s="9">
         <v>445</v>
       </c>
-      <c r="E12" s="10">
+      <c r="E12" s="9">
         <v>445</v>
       </c>
-      <c r="F12" s="10">
+      <c r="F12" s="9">
         <v>445</v>
       </c>
-      <c r="G12" s="10">
+      <c r="G12" s="9">
         <v>445</v>
       </c>
       <c r="H12" s="5"/>
@@ -1068,22 +1074,22 @@
       <c r="A13" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B13" s="9" t="s">
+      <c r="B13" s="8" t="s">
         <v>83</v>
       </c>
-      <c r="C13" s="10">
+      <c r="C13" s="9">
         <v>542.70000000000005</v>
       </c>
-      <c r="D13" s="10">
+      <c r="D13" s="9">
         <v>554.1</v>
       </c>
-      <c r="E13" s="10">
+      <c r="E13" s="9">
         <v>560.5</v>
       </c>
-      <c r="F13" s="10">
+      <c r="F13" s="9">
         <v>567.6</v>
       </c>
-      <c r="G13" s="10">
+      <c r="G13" s="9">
         <v>587</v>
       </c>
       <c r="H13" s="5"/>
@@ -1100,22 +1106,22 @@
       <c r="A14" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="B14" s="9" t="s">
+      <c r="B14" s="8" t="s">
         <v>84</v>
       </c>
-      <c r="C14" s="10">
+      <c r="C14" s="9">
         <v>527.29999999999995</v>
       </c>
-      <c r="D14" s="10">
+      <c r="D14" s="9">
         <v>534.70000000000005</v>
       </c>
-      <c r="E14" s="10">
+      <c r="E14" s="9">
         <v>539</v>
       </c>
-      <c r="F14" s="10">
+      <c r="F14" s="9">
         <v>545.70000000000005</v>
       </c>
-      <c r="G14" s="10">
+      <c r="G14" s="9">
         <v>565.20000000000005</v>
       </c>
       <c r="H14" s="5"/>
@@ -1132,22 +1138,22 @@
       <c r="A15" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B15" s="9" t="s">
+      <c r="B15" s="8" t="s">
         <v>85</v>
       </c>
-      <c r="C15" s="10">
+      <c r="C15" s="9">
         <v>606</v>
       </c>
-      <c r="D15" s="10">
+      <c r="D15" s="9">
         <v>614.4</v>
       </c>
-      <c r="E15" s="10">
+      <c r="E15" s="9">
         <v>623.79999999999995</v>
       </c>
-      <c r="F15" s="10">
+      <c r="F15" s="9">
         <v>633.1</v>
       </c>
-      <c r="G15" s="10">
+      <c r="G15" s="9">
         <v>654.5</v>
       </c>
       <c r="H15" s="5"/>
@@ -1164,22 +1170,22 @@
       <c r="A16" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B16" s="9" t="s">
+      <c r="B16" s="8" t="s">
         <v>86</v>
       </c>
-      <c r="C16" s="10">
+      <c r="C16" s="9">
         <v>366.6</v>
       </c>
-      <c r="D16" s="10">
+      <c r="D16" s="9">
         <v>375.7</v>
       </c>
-      <c r="E16" s="10">
+      <c r="E16" s="9">
         <v>379.4</v>
       </c>
-      <c r="F16" s="10">
+      <c r="F16" s="9">
         <v>384</v>
       </c>
-      <c r="G16" s="10">
+      <c r="G16" s="9">
         <v>397.4</v>
       </c>
       <c r="H16" s="5"/>
@@ -1196,43 +1202,43 @@
       <c r="A17" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="B17" s="9" t="s">
+      <c r="B17" s="8" t="s">
         <v>113</v>
       </c>
-      <c r="C17" s="10">
+      <c r="C17" s="9">
         <f>I17*10</f>
         <v>740</v>
       </c>
-      <c r="D17" s="10">
+      <c r="D17" s="9">
         <f t="shared" ref="D17:G17" si="0">J17*10</f>
         <v>765</v>
       </c>
-      <c r="E17" s="10">
+      <c r="E17" s="9">
         <f t="shared" si="0"/>
         <v>790</v>
       </c>
-      <c r="F17" s="10">
+      <c r="F17" s="9">
         <f t="shared" si="0"/>
         <v>825</v>
       </c>
-      <c r="G17" s="10">
+      <c r="G17" s="9">
         <f t="shared" si="0"/>
         <v>865</v>
       </c>
       <c r="H17" s="5"/>
-      <c r="I17" s="10">
+      <c r="I17" s="9">
         <v>74</v>
       </c>
-      <c r="J17" s="10">
+      <c r="J17" s="9">
         <v>76.5</v>
       </c>
-      <c r="K17" s="10">
+      <c r="K17" s="9">
         <v>79</v>
       </c>
-      <c r="L17" s="10">
+      <c r="L17" s="9">
         <v>82.5</v>
       </c>
-      <c r="M17" s="10">
+      <c r="M17" s="9">
         <v>86.5</v>
       </c>
       <c r="N17" s="6"/>
@@ -1243,43 +1249,43 @@
       <c r="A18" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B18" s="9" t="s">
+      <c r="B18" s="8" t="s">
         <v>114</v>
       </c>
-      <c r="C18" s="10">
+      <c r="C18" s="9">
         <f>I18*10</f>
         <v>760</v>
       </c>
-      <c r="D18" s="10">
+      <c r="D18" s="9">
         <f t="shared" ref="D18" si="1">J18*10</f>
         <v>785</v>
       </c>
-      <c r="E18" s="10">
+      <c r="E18" s="9">
         <f t="shared" ref="E18" si="2">K18*10</f>
         <v>810</v>
       </c>
-      <c r="F18" s="10">
+      <c r="F18" s="9">
         <f t="shared" ref="F18" si="3">L18*10</f>
         <v>845</v>
       </c>
-      <c r="G18" s="10">
+      <c r="G18" s="9">
         <f t="shared" ref="G18" si="4">M18*10</f>
         <v>885</v>
       </c>
       <c r="H18" s="5"/>
-      <c r="I18" s="10">
+      <c r="I18" s="9">
         <v>76</v>
       </c>
-      <c r="J18" s="10">
+      <c r="J18" s="9">
         <v>78.5</v>
       </c>
-      <c r="K18" s="10">
+      <c r="K18" s="9">
         <v>81</v>
       </c>
-      <c r="L18" s="10">
+      <c r="L18" s="9">
         <v>84.5</v>
       </c>
-      <c r="M18" s="10">
+      <c r="M18" s="9">
         <v>88.5</v>
       </c>
       <c r="N18" s="6"/>
@@ -1290,22 +1296,22 @@
       <c r="A19" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B19" s="9" t="s">
+      <c r="B19" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="C19" s="10">
+      <c r="C19" s="9">
         <v>50</v>
       </c>
-      <c r="D19" s="10">
+      <c r="D19" s="9">
         <v>50</v>
       </c>
-      <c r="E19" s="10">
+      <c r="E19" s="9">
         <v>50</v>
       </c>
-      <c r="F19" s="10">
+      <c r="F19" s="9">
         <v>50</v>
       </c>
-      <c r="G19" s="10">
+      <c r="G19" s="9">
         <v>50</v>
       </c>
       <c r="H19" s="5"/>
@@ -1322,22 +1328,22 @@
       <c r="A20" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="B20" s="9" t="s">
+      <c r="B20" s="8" t="s">
         <v>88</v>
       </c>
-      <c r="C20" s="10">
+      <c r="C20" s="9">
         <v>89.6</v>
       </c>
-      <c r="D20" s="10">
+      <c r="D20" s="9">
         <v>89.6</v>
       </c>
-      <c r="E20" s="10">
+      <c r="E20" s="9">
         <v>89.6</v>
       </c>
-      <c r="F20" s="10">
+      <c r="F20" s="9">
         <v>89.6</v>
       </c>
-      <c r="G20" s="10">
+      <c r="G20" s="9">
         <v>82.6</v>
       </c>
       <c r="H20" s="5"/>
@@ -1354,86 +1360,86 @@
       <c r="A21" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="B21" s="9" t="s">
+      <c r="B21" s="8" t="s">
         <v>115</v>
       </c>
-      <c r="C21" s="10">
+      <c r="C21" s="9">
         <v>89.6</v>
       </c>
-      <c r="D21" s="10">
+      <c r="D21" s="9">
         <v>89.6</v>
       </c>
-      <c r="E21" s="10">
+      <c r="E21" s="9">
         <v>89.6</v>
       </c>
-      <c r="F21" s="10">
+      <c r="F21" s="9">
         <v>89.6</v>
       </c>
-      <c r="G21" s="10">
+      <c r="G21" s="9">
         <v>82.6</v>
       </c>
       <c r="H21" s="5"/>
-      <c r="I21" s="8"/>
-      <c r="J21" s="8"/>
-      <c r="K21" s="8"/>
-      <c r="L21" s="8"/>
-      <c r="M21" s="8"/>
-      <c r="N21" s="8"/>
-      <c r="O21" s="8"/>
-      <c r="P21" s="8"/>
+      <c r="I21" s="11"/>
+      <c r="J21" s="11"/>
+      <c r="K21" s="11"/>
+      <c r="L21" s="11"/>
+      <c r="M21" s="11"/>
+      <c r="N21" s="11"/>
+      <c r="O21" s="11"/>
+      <c r="P21" s="11"/>
     </row>
     <row r="22" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B22" s="9" t="s">
+      <c r="B22" s="8" t="s">
         <v>89</v>
       </c>
-      <c r="C22" s="10">
+      <c r="C22" s="9">
         <v>483</v>
       </c>
-      <c r="D22" s="10">
+      <c r="D22" s="9">
         <v>483</v>
       </c>
-      <c r="E22" s="10">
+      <c r="E22" s="9">
         <v>483</v>
       </c>
-      <c r="F22" s="10">
+      <c r="F22" s="9">
         <v>483</v>
       </c>
-      <c r="G22" s="10">
+      <c r="G22" s="9">
         <v>483</v>
       </c>
       <c r="H22" s="7"/>
-      <c r="I22" s="8"/>
-      <c r="J22" s="8"/>
-      <c r="K22" s="8"/>
-      <c r="L22" s="8"/>
-      <c r="M22" s="8"/>
-      <c r="N22" s="8"/>
-      <c r="O22" s="8"/>
-      <c r="P22" s="8"/>
+      <c r="I22" s="11"/>
+      <c r="J22" s="11"/>
+      <c r="K22" s="11"/>
+      <c r="L22" s="11"/>
+      <c r="M22" s="11"/>
+      <c r="N22" s="11"/>
+      <c r="O22" s="11"/>
+      <c r="P22" s="11"/>
     </row>
     <row r="23" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B23" s="9" t="s">
+      <c r="B23" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="C23" s="10">
+      <c r="C23" s="9">
         <v>69</v>
       </c>
-      <c r="D23" s="10">
+      <c r="D23" s="9">
         <v>69</v>
       </c>
-      <c r="E23" s="10">
+      <c r="E23" s="9">
         <v>69</v>
       </c>
-      <c r="F23" s="10">
+      <c r="F23" s="9">
         <v>69</v>
       </c>
-      <c r="G23" s="10">
+      <c r="G23" s="9">
         <v>70</v>
       </c>
       <c r="H23" s="5"/>
@@ -1450,22 +1456,22 @@
       <c r="A24" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B24" s="9" t="s">
+      <c r="B24" s="8" t="s">
         <v>91</v>
       </c>
-      <c r="C24" s="10">
+      <c r="C24" s="9">
         <v>100</v>
       </c>
-      <c r="D24" s="10">
+      <c r="D24" s="9">
         <v>110</v>
       </c>
-      <c r="E24" s="10">
+      <c r="E24" s="9">
         <v>120</v>
       </c>
-      <c r="F24" s="10">
+      <c r="F24" s="9">
         <v>130</v>
       </c>
-      <c r="G24" s="10">
+      <c r="G24" s="9">
         <v>150</v>
       </c>
       <c r="H24" s="5"/>
@@ -1482,22 +1488,22 @@
       <c r="A25" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B25" s="9" t="s">
+      <c r="B25" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="C25" s="10">
+      <c r="C25" s="9">
         <v>74</v>
       </c>
-      <c r="D25" s="10">
+      <c r="D25" s="9">
         <v>74</v>
       </c>
-      <c r="E25" s="10">
+      <c r="E25" s="9">
         <v>74</v>
       </c>
-      <c r="F25" s="10">
+      <c r="F25" s="9">
         <v>74</v>
       </c>
-      <c r="G25" s="10">
+      <c r="G25" s="9">
         <v>74</v>
       </c>
       <c r="H25" s="5"/>
@@ -1514,22 +1520,22 @@
       <c r="A26" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B26" s="9" t="s">
+      <c r="B26" s="8" t="s">
         <v>93</v>
       </c>
-      <c r="C26" s="10">
+      <c r="C26" s="9">
         <v>1062.0999999999999</v>
       </c>
-      <c r="D26" s="10">
+      <c r="D26" s="9">
         <v>1075</v>
       </c>
-      <c r="E26" s="10">
+      <c r="E26" s="9">
         <v>1082.3</v>
       </c>
-      <c r="F26" s="10">
+      <c r="F26" s="9">
         <v>1090.2</v>
       </c>
-      <c r="G26" s="10">
+      <c r="G26" s="9">
         <v>1101.3</v>
       </c>
       <c r="H26" s="5"/>
@@ -1546,22 +1552,22 @@
       <c r="A27" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B27" s="9" t="s">
+      <c r="B27" s="8" t="s">
         <v>94</v>
       </c>
-      <c r="C27" s="10">
+      <c r="C27" s="9">
         <v>420</v>
       </c>
-      <c r="D27" s="10">
+      <c r="D27" s="9">
         <v>440</v>
       </c>
-      <c r="E27" s="10">
+      <c r="E27" s="9">
         <v>460</v>
       </c>
-      <c r="F27" s="10">
+      <c r="F27" s="9">
         <v>460</v>
       </c>
-      <c r="G27" s="10">
+      <c r="G27" s="9">
         <v>480</v>
       </c>
       <c r="H27" s="5"/>
@@ -1578,22 +1584,22 @@
       <c r="A28" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="B28" s="9" t="s">
+      <c r="B28" s="8" t="s">
         <v>95</v>
       </c>
-      <c r="C28" s="10">
+      <c r="C28" s="9">
         <v>628.29999999999995</v>
       </c>
-      <c r="D28" s="10">
+      <c r="D28" s="9">
         <v>640.70000000000005</v>
       </c>
-      <c r="E28" s="10">
+      <c r="E28" s="9">
         <v>648</v>
       </c>
-      <c r="F28" s="10">
+      <c r="F28" s="9">
         <v>656</v>
       </c>
-      <c r="G28" s="10">
+      <c r="G28" s="9">
         <v>666.3</v>
       </c>
       <c r="H28" s="5"/>
@@ -1608,24 +1614,24 @@
     </row>
     <row r="29" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="B29" s="9" t="s">
+        <v>126</v>
+      </c>
+      <c r="B29" s="8" t="s">
         <v>96</v>
       </c>
-      <c r="C29" s="10">
+      <c r="C29" s="9">
         <v>148</v>
       </c>
-      <c r="D29" s="10">
+      <c r="D29" s="9">
         <v>148</v>
       </c>
-      <c r="E29" s="10">
+      <c r="E29" s="9">
         <v>148</v>
       </c>
-      <c r="F29" s="10">
+      <c r="F29" s="9">
         <v>148</v>
       </c>
-      <c r="G29" s="10">
+      <c r="G29" s="9">
         <v>148</v>
       </c>
       <c r="H29" s="5"/>
@@ -1642,22 +1648,22 @@
       <c r="A30" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B30" s="9" t="s">
+      <c r="B30" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="C30" s="10">
+      <c r="C30" s="9">
         <v>2100</v>
       </c>
-      <c r="D30" s="10">
+      <c r="D30" s="9">
         <v>2180</v>
       </c>
-      <c r="E30" s="10">
+      <c r="E30" s="9">
         <v>2260</v>
       </c>
-      <c r="F30" s="10">
+      <c r="F30" s="9">
         <v>2400</v>
       </c>
-      <c r="G30" s="10">
+      <c r="G30" s="9">
         <v>2480</v>
       </c>
       <c r="H30" s="5"/>
@@ -1674,22 +1680,22 @@
       <c r="A31" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="B31" s="9" t="s">
+      <c r="B31" s="8" t="s">
         <v>116</v>
       </c>
-      <c r="C31" s="10">
+      <c r="C31" s="9">
         <v>700</v>
       </c>
-      <c r="D31" s="10">
+      <c r="D31" s="9">
         <v>700</v>
       </c>
-      <c r="E31" s="10">
+      <c r="E31" s="9">
         <v>700</v>
       </c>
-      <c r="F31" s="10">
+      <c r="F31" s="9">
         <v>700</v>
       </c>
-      <c r="G31" s="10">
+      <c r="G31" s="9">
         <v>700</v>
       </c>
       <c r="H31" s="5"/>
@@ -1706,22 +1712,22 @@
       <c r="A32" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B32" s="9" t="s">
+      <c r="B32" s="8" t="s">
         <v>99</v>
       </c>
-      <c r="C32" s="10">
+      <c r="C32" s="9">
         <v>70</v>
       </c>
-      <c r="D32" s="10">
+      <c r="D32" s="9">
         <v>70</v>
       </c>
-      <c r="E32" s="10">
+      <c r="E32" s="9">
         <v>80</v>
       </c>
-      <c r="F32" s="10">
+      <c r="F32" s="9">
         <v>90</v>
       </c>
-      <c r="G32" s="10">
+      <c r="G32" s="9">
         <v>100</v>
       </c>
       <c r="H32" s="5"/>
@@ -1738,246 +1744,249 @@
       <c r="A33" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B33" s="9" t="s">
+      <c r="B33" s="8" t="s">
         <v>100</v>
       </c>
-      <c r="C33" s="10">
+      <c r="C33" s="9">
         <v>170</v>
       </c>
-      <c r="D33" s="10">
+      <c r="D33" s="9">
         <v>170</v>
       </c>
-      <c r="E33" s="10">
+      <c r="E33" s="9">
         <v>170</v>
       </c>
-      <c r="F33" s="10">
+      <c r="F33" s="9">
         <v>170</v>
       </c>
-      <c r="G33" s="10">
+      <c r="G33" s="9">
         <v>175</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A34" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B34" s="11"/>
-      <c r="C34" s="10">
-        <v>700</v>
-      </c>
-      <c r="D34" s="10">
-        <v>700</v>
-      </c>
-      <c r="E34" s="10">
-        <v>700</v>
-      </c>
-      <c r="F34" s="10">
-        <v>700</v>
-      </c>
-      <c r="G34" s="10">
-        <v>700</v>
+        <v>137</v>
+      </c>
+      <c r="B34" s="8"/>
+      <c r="C34" s="9">
+        <v>0</v>
+      </c>
+      <c r="D34" s="9">
+        <v>0</v>
+      </c>
+      <c r="E34" s="9">
+        <v>0</v>
+      </c>
+      <c r="F34" s="9">
+        <v>0</v>
+      </c>
+      <c r="G34" s="9">
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A35" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="B35" s="8"/>
+      <c r="C35" s="9">
+        <v>0</v>
+      </c>
+      <c r="D35" s="9">
+        <v>0</v>
+      </c>
+      <c r="E35" s="9">
+        <v>0</v>
+      </c>
+      <c r="F35" s="9">
+        <v>0</v>
+      </c>
+      <c r="G35" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A36" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B36" s="10"/>
+      <c r="C36" s="9">
+        <v>700</v>
+      </c>
+      <c r="D36" s="9">
+        <v>700</v>
+      </c>
+      <c r="E36" s="9">
+        <v>700</v>
+      </c>
+      <c r="F36" s="9">
+        <v>700</v>
+      </c>
+      <c r="G36" s="9">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A37" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B35" s="9"/>
-      <c r="C35" s="10">
+      <c r="B37" s="8"/>
+      <c r="C37" s="9">
         <f>2.4*25.4</f>
         <v>60.959999999999994</v>
       </c>
-      <c r="D35" s="10">
-        <f t="shared" ref="D35:G35" si="5">2.4*25.4</f>
+      <c r="D37" s="9">
+        <f t="shared" ref="D37:G37" si="5">2.4*25.4</f>
         <v>60.959999999999994</v>
       </c>
-      <c r="E35" s="10">
+      <c r="E37" s="9">
         <f t="shared" si="5"/>
         <v>60.959999999999994</v>
       </c>
-      <c r="F35" s="10">
+      <c r="F37" s="9">
         <f t="shared" si="5"/>
         <v>60.959999999999994</v>
       </c>
-      <c r="G35" s="10">
+      <c r="G37" s="9">
         <f t="shared" si="5"/>
         <v>60.959999999999994</v>
       </c>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A36" s="1" t="s">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A38" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="B36" s="9"/>
-      <c r="C36" s="11">
+      <c r="B38" s="8"/>
+      <c r="C38" s="10">
         <f>2.6*24.5</f>
         <v>63.7</v>
       </c>
-      <c r="D36" s="11">
-        <f t="shared" ref="D36:G36" si="6">2.6*24.5</f>
+      <c r="D38" s="10">
+        <f t="shared" ref="D38:G38" si="6">2.6*24.5</f>
         <v>63.7</v>
       </c>
-      <c r="E36" s="11">
+      <c r="E38" s="10">
         <f t="shared" si="6"/>
         <v>63.7</v>
       </c>
-      <c r="F36" s="11">
+      <c r="F38" s="10">
         <f t="shared" si="6"/>
         <v>63.7</v>
       </c>
-      <c r="G36" s="11">
+      <c r="G38" s="10">
         <f t="shared" si="6"/>
         <v>63.7</v>
       </c>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A37" s="1" t="s">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A39" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B37" s="9"/>
-      <c r="C37" s="11">
-        <f>C39</f>
+      <c r="B39" s="8"/>
+      <c r="C39" s="10">
+        <f>C41</f>
         <v>151</v>
       </c>
-      <c r="D37" s="11">
-        <f>AVERAGE(D39,C40)</f>
+      <c r="D39" s="10">
+        <f>AVERAGE(D41,C42)</f>
         <v>162.5</v>
       </c>
-      <c r="E37" s="11">
-        <f t="shared" ref="E37:G37" si="7">AVERAGE(E39,D40)</f>
+      <c r="E39" s="10">
+        <f t="shared" ref="E39:G39" si="7">AVERAGE(E41,D42)</f>
         <v>172</v>
       </c>
-      <c r="F37" s="11">
+      <c r="F39" s="10">
         <f t="shared" si="7"/>
         <v>181.5</v>
       </c>
-      <c r="G37" s="11">
+      <c r="G39" s="10">
         <f t="shared" si="7"/>
         <v>189</v>
       </c>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A38" s="1" t="s">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A40" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B38" s="9"/>
-      <c r="C38" s="11">
-        <f>D37</f>
+      <c r="B40" s="8"/>
+      <c r="C40" s="10">
+        <f>D39</f>
         <v>162.5</v>
       </c>
-      <c r="D38" s="11">
-        <f t="shared" ref="D38:F38" si="8">E37</f>
+      <c r="D40" s="10">
+        <f t="shared" ref="D40:F40" si="8">E39</f>
         <v>172</v>
       </c>
-      <c r="E38" s="11">
+      <c r="E40" s="10">
         <f t="shared" si="8"/>
         <v>181.5</v>
       </c>
-      <c r="F38" s="11">
+      <c r="F40" s="10">
         <f t="shared" si="8"/>
         <v>189</v>
       </c>
-      <c r="G38" s="11">
-        <f>G40</f>
+      <c r="G40" s="10">
+        <f>G42</f>
         <v>198</v>
       </c>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A39" s="1" t="s">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A41" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="B39" s="9"/>
-      <c r="C39" s="11">
+      <c r="B41" s="8"/>
+      <c r="C41" s="10">
         <v>151</v>
       </c>
-      <c r="D39" s="11">
+      <c r="D41" s="10">
         <v>162</v>
       </c>
-      <c r="E39" s="11">
+      <c r="E41" s="10">
         <v>170</v>
       </c>
-      <c r="F39" s="11">
+      <c r="F41" s="10">
         <v>180</v>
       </c>
-      <c r="G39" s="11">
+      <c r="G41" s="10">
         <v>188</v>
       </c>
-    </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A40" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="B40" s="9"/>
-      <c r="C40" s="11">
-        <v>163</v>
-      </c>
-      <c r="D40" s="11">
-        <v>174</v>
-      </c>
-      <c r="E40" s="11">
-        <v>183</v>
-      </c>
-      <c r="F40" s="11">
-        <v>190</v>
-      </c>
-      <c r="G40" s="11">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A41" s="1"/>
-      <c r="B41" s="1"/>
-      <c r="C41" s="1"/>
-      <c r="D41" s="1"/>
-      <c r="E41" s="1"/>
-      <c r="F41" s="1"/>
-      <c r="G41" s="1"/>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A42" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B42" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C42" s="1"/>
-      <c r="D42" s="1"/>
-      <c r="E42" s="1"/>
-      <c r="F42" s="1"/>
-      <c r="G42" s="1"/>
+        <v>106</v>
+      </c>
+      <c r="B42" s="8"/>
+      <c r="C42" s="10">
+        <v>163</v>
+      </c>
+      <c r="D42" s="10">
+        <v>174</v>
+      </c>
+      <c r="E42" s="10">
+        <v>183</v>
+      </c>
+      <c r="F42" s="10">
+        <v>190</v>
+      </c>
+      <c r="G42" s="10">
+        <v>198</v>
+      </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A43" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="B43" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="C43" s="6" t="s">
-        <v>117</v>
-      </c>
-      <c r="D43" s="6" t="s">
-        <v>118</v>
-      </c>
-      <c r="E43" s="6" t="s">
-        <v>119</v>
-      </c>
-      <c r="F43" s="6" t="s">
-        <v>120</v>
-      </c>
-      <c r="G43" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="H43" s="5" t="s">
-        <v>97</v>
-      </c>
+      <c r="A43" s="1"/>
+      <c r="B43" s="1"/>
+      <c r="C43" s="1"/>
+      <c r="D43" s="1"/>
+      <c r="E43" s="1"/>
+      <c r="F43" s="1"/>
+      <c r="G43" s="1"/>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A44" s="1" t="s">
-        <v>68</v>
+        <v>29</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>69</v>
+        <v>30</v>
       </c>
       <c r="C44" s="1"/>
       <c r="D44" s="1"/>
@@ -1987,23 +1996,36 @@
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A45" s="1" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="C45" s="3"/>
-      <c r="D45" s="3"/>
-      <c r="E45" s="3"/>
-      <c r="F45" s="3"/>
-      <c r="G45" s="3"/>
+        <v>67</v>
+      </c>
+      <c r="C45" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="D45" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="E45" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="F45" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="G45" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="H45" s="5" t="s">
+        <v>97</v>
+      </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A46" s="1" t="s">
-        <v>31</v>
+        <v>68</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>109</v>
+        <v>69</v>
       </c>
       <c r="C46" s="1"/>
       <c r="D46" s="1"/>
@@ -2013,22 +2035,24 @@
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A47" s="1" t="s">
-        <v>32</v>
+        <v>70</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="C47" s="1"/>
-      <c r="D47" s="1"/>
-      <c r="E47" s="1"/>
-      <c r="F47" s="1"/>
-      <c r="G47" s="1"/>
+        <v>71</v>
+      </c>
+      <c r="C47" s="3"/>
+      <c r="D47" s="3"/>
+      <c r="E47" s="3"/>
+      <c r="F47" s="3"/>
+      <c r="G47" s="3"/>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A48" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B48" s="1"/>
+        <v>31</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>109</v>
+      </c>
       <c r="C48" s="1"/>
       <c r="D48" s="1"/>
       <c r="E48" s="1"/>
@@ -2037,11 +2061,10 @@
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A49" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B49" s="1">
-        <f>2.6*24.5</f>
-        <v>63.7</v>
+        <v>32</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>72</v>
       </c>
       <c r="C49" s="1"/>
       <c r="D49" s="1"/>
@@ -2051,11 +2074,9 @@
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A50" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B50" s="1">
-        <v>2.9</v>
-      </c>
+        <v>33</v>
+      </c>
+      <c r="B50" s="1"/>
       <c r="C50" s="1"/>
       <c r="D50" s="1"/>
       <c r="E50" s="1"/>
@@ -2064,10 +2085,11 @@
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A51" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B51" s="1">
-        <v>100</v>
+        <f>2.6*24.5</f>
+        <v>63.7</v>
       </c>
       <c r="C51" s="1"/>
       <c r="D51" s="1"/>
@@ -2077,57 +2099,57 @@
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A52" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="B52" s="1"/>
+        <v>35</v>
+      </c>
+      <c r="B52" s="1">
+        <v>2.9</v>
+      </c>
       <c r="C52" s="1"/>
       <c r="D52" s="1"/>
-      <c r="E52" s="3"/>
-      <c r="F52" s="3"/>
-      <c r="G52" s="3"/>
+      <c r="E52" s="1"/>
+      <c r="F52" s="1"/>
+      <c r="G52" s="1"/>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A53" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="B53" s="1"/>
-      <c r="C53" s="3"/>
-      <c r="D53" s="3"/>
+        <v>36</v>
+      </c>
+      <c r="B53" s="1">
+        <v>100</v>
+      </c>
+      <c r="C53" s="1"/>
+      <c r="D53" s="1"/>
       <c r="E53" s="1"/>
       <c r="F53" s="1"/>
       <c r="G53" s="1"/>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A54" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B54" s="1"/>
       <c r="C54" s="1"/>
       <c r="D54" s="1"/>
-      <c r="E54" s="1"/>
-      <c r="F54" s="1"/>
-      <c r="G54" s="1"/>
+      <c r="E54" s="3"/>
+      <c r="F54" s="3"/>
+      <c r="G54" s="3"/>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A55" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="B55" s="1">
-        <v>148</v>
-      </c>
-      <c r="C55" s="1"/>
-      <c r="D55" s="1"/>
+        <v>38</v>
+      </c>
+      <c r="B55" s="1"/>
+      <c r="C55" s="3"/>
+      <c r="D55" s="3"/>
       <c r="E55" s="1"/>
       <c r="F55" s="1"/>
       <c r="G55" s="1"/>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A56" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="B56" s="1">
-        <v>110</v>
-      </c>
+        <v>39</v>
+      </c>
+      <c r="B56" s="1"/>
       <c r="C56" s="1"/>
       <c r="D56" s="1"/>
       <c r="E56" s="1"/>
@@ -2136,9 +2158,11 @@
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A57" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="B57" s="1"/>
+        <v>40</v>
+      </c>
+      <c r="B57" s="1">
+        <v>148</v>
+      </c>
       <c r="C57" s="1"/>
       <c r="D57" s="1"/>
       <c r="E57" s="1"/>
@@ -2147,9 +2171,11 @@
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A58" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="B58" s="1"/>
+        <v>41</v>
+      </c>
+      <c r="B58" s="1">
+        <v>110</v>
+      </c>
       <c r="C58" s="1"/>
       <c r="D58" s="1"/>
       <c r="E58" s="1"/>
@@ -2158,7 +2184,7 @@
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A59" s="1" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="B59" s="1"/>
       <c r="C59" s="1"/>
@@ -2169,7 +2195,7 @@
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A60" s="1" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="B60" s="1"/>
       <c r="C60" s="1"/>
@@ -2180,7 +2206,7 @@
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A61" s="1" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="B61" s="1"/>
       <c r="C61" s="1"/>
@@ -2191,7 +2217,7 @@
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A62" s="1" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="B62" s="1"/>
       <c r="C62" s="1"/>
@@ -2202,11 +2228,9 @@
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A63" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B63" s="1" t="s">
-        <v>74</v>
-      </c>
+        <v>135</v>
+      </c>
+      <c r="B63" s="1"/>
       <c r="C63" s="1"/>
       <c r="D63" s="1"/>
       <c r="E63" s="1"/>
@@ -2215,7 +2239,7 @@
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A64" s="1" t="s">
-        <v>43</v>
+        <v>136</v>
       </c>
       <c r="B64" s="1"/>
       <c r="C64" s="1"/>
@@ -2226,10 +2250,10 @@
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A65" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B65" s="1">
-        <v>31.6</v>
+        <v>42</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>74</v>
       </c>
       <c r="C65" s="1"/>
       <c r="D65" s="1"/>
@@ -2239,11 +2263,9 @@
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A66" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="B66" s="1" t="s">
-        <v>124</v>
-      </c>
+        <v>43</v>
+      </c>
+      <c r="B66" s="1"/>
       <c r="C66" s="1"/>
       <c r="D66" s="1"/>
       <c r="E66" s="1"/>
@@ -2252,10 +2274,10 @@
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A67" s="1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B67" s="1">
-        <v>36</v>
+        <v>31.6</v>
       </c>
       <c r="C67" s="1"/>
       <c r="D67" s="1"/>
@@ -2265,9 +2287,11 @@
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A68" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="B68" s="1"/>
+        <v>45</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>124</v>
+      </c>
       <c r="C68" s="1"/>
       <c r="D68" s="1"/>
       <c r="E68" s="1"/>
@@ -2276,10 +2300,10 @@
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A69" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B69" s="1">
-        <v>180</v>
+        <v>36</v>
       </c>
       <c r="C69" s="1"/>
       <c r="D69" s="1"/>
@@ -2289,11 +2313,9 @@
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A70" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="B70" s="1">
-        <v>160</v>
-      </c>
+        <v>47</v>
+      </c>
+      <c r="B70" s="1"/>
       <c r="C70" s="1"/>
       <c r="D70" s="1"/>
       <c r="E70" s="1"/>
@@ -2302,9 +2324,11 @@
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A71" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="B71" s="1"/>
+        <v>48</v>
+      </c>
+      <c r="B71" s="1">
+        <v>180</v>
+      </c>
       <c r="C71" s="1"/>
       <c r="D71" s="1"/>
       <c r="E71" s="1"/>
@@ -2313,10 +2337,10 @@
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A72" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="B72" s="1" t="s">
-        <v>110</v>
+        <v>49</v>
+      </c>
+      <c r="B72" s="1">
+        <v>160</v>
       </c>
       <c r="C72" s="1"/>
       <c r="D72" s="1"/>
@@ -2326,11 +2350,9 @@
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A73" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="B73" s="1" t="s">
-        <v>110</v>
-      </c>
+        <v>50</v>
+      </c>
+      <c r="B73" s="1"/>
       <c r="C73" s="1"/>
       <c r="D73" s="1"/>
       <c r="E73" s="1"/>
@@ -2339,10 +2361,10 @@
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A74" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>72</v>
+        <v>110</v>
       </c>
       <c r="C74" s="1"/>
       <c r="D74" s="1"/>
@@ -2352,9 +2374,11 @@
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A75" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="B75" s="1"/>
+        <v>52</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>110</v>
+      </c>
       <c r="C75" s="1"/>
       <c r="D75" s="1"/>
       <c r="E75" s="1"/>
@@ -2363,10 +2387,10 @@
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A76" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="B76" s="1">
-        <v>2</v>
+        <v>53</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>72</v>
       </c>
       <c r="C76" s="1"/>
       <c r="D76" s="1"/>
@@ -2376,11 +2400,9 @@
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A77" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="B77" s="1">
-        <v>1</v>
-      </c>
+        <v>54</v>
+      </c>
+      <c r="B77" s="1"/>
       <c r="C77" s="1"/>
       <c r="D77" s="1"/>
       <c r="E77" s="1"/>
@@ -2389,10 +2411,10 @@
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A78" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="B78" s="1" t="s">
-        <v>72</v>
+        <v>55</v>
+      </c>
+      <c r="B78" s="1">
+        <v>2</v>
       </c>
       <c r="C78" s="1"/>
       <c r="D78" s="1"/>
@@ -2402,10 +2424,10 @@
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A79" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="B79" s="1" t="s">
-        <v>72</v>
+        <v>56</v>
+      </c>
+      <c r="B79" s="1">
+        <v>1</v>
       </c>
       <c r="C79" s="1"/>
       <c r="D79" s="1"/>
@@ -2415,7 +2437,7 @@
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A80" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B80" s="1" t="s">
         <v>72</v>
@@ -2428,7 +2450,7 @@
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A81" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B81" s="1" t="s">
         <v>72</v>
@@ -2441,7 +2463,7 @@
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A82" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B82" s="1" t="s">
         <v>72</v>
@@ -2454,10 +2476,10 @@
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A83" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="B83" s="1">
-        <v>1795</v>
+        <v>60</v>
+      </c>
+      <c r="B83" s="1" t="s">
+        <v>72</v>
       </c>
       <c r="C83" s="1"/>
       <c r="D83" s="1"/>
@@ -2467,10 +2489,10 @@
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A84" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="B84" s="1">
-        <v>3000</v>
+        <v>61</v>
+      </c>
+      <c r="B84" s="1" t="s">
+        <v>72</v>
       </c>
       <c r="C84" s="1"/>
       <c r="D84" s="1"/>
@@ -2480,10 +2502,10 @@
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A85" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="B85" s="1" t="s">
-        <v>72</v>
+        <v>62</v>
+      </c>
+      <c r="B85" s="1">
+        <v>1795</v>
       </c>
       <c r="C85" s="1"/>
       <c r="D85" s="1"/>
@@ -2493,10 +2515,10 @@
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A86" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="B86" s="1" t="s">
-        <v>128</v>
+        <v>63</v>
+      </c>
+      <c r="B86" s="1">
+        <v>3000</v>
       </c>
       <c r="C86" s="1"/>
       <c r="D86" s="1"/>
@@ -2505,11 +2527,37 @@
       <c r="G86" s="1"/>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A87" t="s">
+      <c r="A87" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B87" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="C87" s="1"/>
+      <c r="D87" s="1"/>
+      <c r="E87" s="1"/>
+      <c r="F87" s="1"/>
+      <c r="G87" s="1"/>
+    </row>
+    <row r="88" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A88" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B88" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="C88" s="1"/>
+      <c r="D88" s="1"/>
+      <c r="E88" s="1"/>
+      <c r="F88" s="1"/>
+      <c r="G88" s="1"/>
+    </row>
+    <row r="89" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A89" t="s">
+        <v>129</v>
+      </c>
+      <c r="B89" t="s">
         <v>130</v>
-      </c>
-      <c r="B87" t="s">
-        <v>131</v>
       </c>
     </row>
   </sheetData>
